--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/o-higgins.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/o-higgins.xlsx
@@ -757,7 +757,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1781,7 +1785,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1972,7 +1980,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2293,7 +2305,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2419,7 +2435,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2732,7 +2752,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3244,7 +3268,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3366,7 +3394,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3492,7 +3524,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3744,7 +3780,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5857,7 +5897,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6690,7 +6734,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8730,7 +8778,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10270,7 +10322,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10522,7 +10578,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10774,7 +10834,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11152,7 +11216,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11538,7 +11606,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12944,7 +13016,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13005,7 +13081,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13326,7 +13406,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15163,7 +15247,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16695,7 +16783,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17207,7 +17299,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +17746,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17776,7 +17876,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17902,7 +18006,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17963,7 +18071,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18284,7 +18396,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19044,7 +19160,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19105,7 +19225,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19296,7 +19420,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20251,7 +20379,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20629,7 +20761,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20946,7 +21082,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21328,7 +21468,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23120,7 +23264,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +23650,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24400,7 +24552,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24461,7 +24617,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24782,7 +24942,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24908,7 +25072,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25095,7 +25263,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25924,7 +26096,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27265,7 +27441,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27456,7 +27636,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30975,7 +31159,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32592,7 +32780,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32783,7 +32975,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32844,7 +33040,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32905,7 +33105,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34254,7 +34458,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36119,7 +36327,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36822,7 +37034,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39203,7 +39419,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39650,7 +39870,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39971,7 +40195,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40162,7 +40390,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41186,7 +41418,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41889,7 +42125,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42015,7 +42255,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42271,7 +42515,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42527,7 +42775,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43234,7 +43486,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43425,7 +43681,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43937,7 +44197,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44380,7 +44644,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44441,7 +44709,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45140,7 +45412,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45396,7 +45672,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45522,7 +45802,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45713,7 +45997,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47176,7 +47464,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47623,7 +47915,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47940,7 +48236,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48261,7 +48561,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48948,7 +49252,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49009,7 +49317,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49265,7 +49577,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50545,7 +50861,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51374,7 +51694,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51951,7 +52275,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52857,7 +53185,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53369,7 +53701,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L829" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53621,7 +53957,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53877,7 +54217,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54133,7 +54477,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L841" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56067,7 +56415,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L871" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56323,7 +56675,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L875" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58781,7 +59137,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L913" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58842,7 +59202,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59033,7 +59397,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L917" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59740,7 +60108,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L928" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59931,7 +60303,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L931" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60179,7 +60555,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60431,7 +60811,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L939" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61577,7 +61961,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K957" t="inlineStr"/>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L957" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63454,7 +63842,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K986" t="inlineStr"/>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L986" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64027,7 +64419,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K995" t="inlineStr"/>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L995" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64413,7 +64809,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1001" t="inlineStr"/>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1001" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64604,7 +65004,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1004" t="inlineStr"/>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1004" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64726,7 +65130,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1006" t="inlineStr"/>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1006" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64982,7 +65390,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1010" t="inlineStr"/>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1010" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65043,7 +65455,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1011" t="inlineStr"/>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1011" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65104,7 +65520,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1012" t="inlineStr"/>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1012" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65742,7 +66162,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1022" t="inlineStr"/>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1022" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67416,7 +67840,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1048" t="inlineStr"/>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1048" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68058,7 +68486,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1058" t="inlineStr"/>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1058" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68184,7 +68616,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1060" t="inlineStr"/>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1060" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68310,7 +68746,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1062" t="inlineStr"/>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1062" t="inlineStr">
         <is>
           <t>USD</t>
